--- a/apiHirams/resources/templates/VoucherTemplate.xlsx
+++ b/apiHirams/resources/templates/VoucherTemplate.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Program\hirams\apiHirams\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B592B11-1A21-4B67-BE44-9CF83DB640B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D32077-CC91-41BB-9AB3-80E5D703FA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2DA72AEB-AFE0-4E7E-B21D-141FAD65A820}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$N$27</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -137,9 +140,6 @@
     <t xml:space="preserve">Prepared By: </t>
   </si>
   <si>
-    <t>Less:  EWT/DISC/ CA</t>
-  </si>
-  <si>
     <t>TIN:</t>
   </si>
   <si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>NO. DV:</t>
+  </si>
+  <si>
+    <t>Less:  EWT/DISC</t>
   </si>
 </sst>
 </file>
@@ -452,6 +455,141 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -470,9 +608,6 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -491,143 +626,11 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -971,10 +974,10 @@
     <col min="2" max="3" width="8.88671875" style="1"/>
     <col min="4" max="5" width="1.21875" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="3.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="8.5546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="7.6640625" style="1" customWidth="1"/>
     <col min="13" max="13" width="6.109375" style="1" customWidth="1"/>
@@ -986,89 +989,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="24"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="68"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="62"/>
       <c r="J2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="20"/>
+        <v>35</v>
+      </c>
+      <c r="K2" s="63"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="65"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="62"/>
       <c r="J3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="31"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
+        <v>32</v>
+      </c>
+      <c r="K3" s="37"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
     </row>
     <row r="4" spans="1:14" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
       <c r="H5" s="4" t="s">
         <v>2</v>
       </c>
@@ -1078,83 +1081,83 @@
       <c r="J5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="33" t="s">
+      <c r="K5" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
+      <c r="A6" s="73"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="50"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
+      <c r="A7" s="40"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
       <c r="H7" s="9"/>
       <c r="I7" s="6"/>
       <c r="J7" s="7"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="A8" s="40"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
       <c r="H8" s="10"/>
       <c r="I8" s="11"/>
       <c r="J8" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="38"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
       <c r="H9" s="13"/>
-      <c r="I9" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
+      <c r="I9" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="45"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="50"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="51" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="52"/>
@@ -1163,327 +1166,378 @@
       <c r="E10" s="52"/>
       <c r="F10" s="52"/>
       <c r="G10" s="52"/>
-      <c r="H10" s="72" t="s">
+      <c r="H10" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="73"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
     </row>
     <row r="11" spans="1:14" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="33" t="s">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="33" t="s">
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="54"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="37"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
     </row>
     <row r="17" spans="1:14" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="48" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
       <c r="K18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="37"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="47" t="s">
+      <c r="A19" s="37"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
       <c r="J19" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M19" s="49" t="s">
+      <c r="M19" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="N19" s="50"/>
+      <c r="N19" s="43"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="53"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="42" t="s">
+      <c r="A20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="L20" s="42"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="67" t="s">
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
     </row>
     <row r="22" spans="1:14" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="56"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="58"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="43" t="s">
+      <c r="B23" s="25"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="65"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="43" t="s">
+      <c r="G23" s="26"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="L23" s="65"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="71"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="42"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="53"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="37"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="28" t="s">
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="27"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="71"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="64"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="23"/>
       <c r="F26" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="49"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="50"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="43"/>
       <c r="K26" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="L26" s="45"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
     </row>
     <row r="27" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="67">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="A17:N17"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="F20:J20"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="F22:N22"/>
     <mergeCell ref="D18:E26"/>
@@ -1500,57 +1554,6 @@
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="K23:L23"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="A17:N17"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="B3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="portrait" r:id="rId1"/>
